--- a/output/pdf_financials_xlsx/NIX.xlsx
+++ b/output/pdf_financials_xlsx/NIX.xlsx
@@ -1916,13 +1916,13 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>3.206065</v>
+        <v>6.595125</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>3.836653</v>
+        <v>8.197926000000001</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>3.511175</v>
+        <v>8.470294000000001</v>
       </c>
     </row>
     <row r="93">
@@ -3104,7 +3104,11 @@
           <t>Warrants reserve 12</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -3552,7 +3556,11 @@
           <t>Warrants reserve 15</t>
         </is>
       </c>
-      <c r="D29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
         <v>3.38906</v>
       </c>

--- a/output/pdf_financials_xlsx/NIX.xlsx
+++ b/output/pdf_financials_xlsx/NIX.xlsx
@@ -609,13 +609,13 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>0.2289</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.047905</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.052959</v>
       </c>
     </row>
     <row r="13">
@@ -861,13 +861,13 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-3.286535</v>
+        <v>-3.515435</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-35.793864</v>
+        <v>-35.841769</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.246241</v>
+        <v>-1.2992</v>
       </c>
     </row>
     <row r="28">
@@ -893,13 +893,13 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-3.282585</v>
+        <v>-3.511485</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-35.790705</v>
+        <v>-35.83861</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.246228</v>
+        <v>-1.299187</v>
       </c>
     </row>
     <row r="30">
@@ -976,13 +976,13 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>2.876128</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.875556</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>1.062234</v>
       </c>
     </row>
     <row r="35">
@@ -1008,13 +1008,13 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>2.876128</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.875556</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>1.062234</v>
       </c>
     </row>
     <row r="37">
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>3.005477</v>
+        <v>0.129349</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>3.587054</v>
+        <v>2.711498</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>1.108071</v>
+        <v>0.045837</v>
       </c>
     </row>
     <row r="49">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -6791,7 +6791,7 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -6824,7 +6824,7 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -7299,7 +7299,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E148" s="5" t="n">
@@ -7332,7 +7332,7 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E149" s="5" t="n">

--- a/output/pdf_financials_xlsx/NIX.xlsx
+++ b/output/pdf_financials_xlsx/NIX.xlsx
@@ -1510,13 +1510,13 @@
         </is>
       </c>
       <c r="B67" s="3" t="n">
-        <v>0</v>
+        <v>0.076139</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.056025</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.073</v>
       </c>
     </row>
     <row r="68">
@@ -1526,13 +1526,13 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0.739549</v>
+        <v>0.815688</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0.147366</v>
+        <v>0.203391</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0.094927</v>
+        <v>0.167927</v>
       </c>
     </row>
     <row r="69">
@@ -1638,10 +1638,10 @@
         </is>
       </c>
       <c r="B75" s="3" t="n">
-        <v>0.5263099999999999</v>
+        <v>0.450171</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>2.655709</v>
+        <v>2.599684</v>
       </c>
       <c r="D75" s="3" t="n">
         <v>0</v>
@@ -2211,10 +2211,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.019564</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.0123</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -2585,10 +2585,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.019564</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.0123</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -2601,10 +2601,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-2.428748</v>
+        <v>-2.448312</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-1.351001</v>
+        <v>-1.363301</v>
       </c>
       <c r="D135" s="3" t="n">
         <v>-0.957241</v>
@@ -4089,7 +4089,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E46" s="5" t="n">
         <v>-0.019564</v>
       </c>
@@ -5279,7 +5283,11 @@
           <t>Deferred income tax expense (recovery)</t>
         </is>
       </c>
-      <c r="D84" t="inlineStr"/>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>DeferredTax</t>
+        </is>
+      </c>
       <c r="E84" s="5" t="n">
         <v>0.051</v>
       </c>
